--- a/exports/coquinhaEnzo.xlsx
+++ b/exports/coquinhaEnzo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,81 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pagante</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02/01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20/02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10/04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Enzo</t>
         </is>
       </c>
     </row>
